--- a/src/xlsx/dex.xlsx
+++ b/src/xlsx/dex.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/pokegoldCHS/src/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19075592-1BD7-0043-B1CC-9D748CC31522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6668A75-9274-AB40-A22E-6E433D05F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18100" yWindow="1060" windowWidth="23760" windowHeight="23340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
